--- a/data/trans_dic/P2A_psíq_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2A_psíq_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad psíquica</t>
+          <t>Hogares con personas con limitación por discapacidad psíquica (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 4,08</t>
+          <t>0,36; 4,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,33; 7,88</t>
+          <t>2,26; 7,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 5,29</t>
+          <t>1,12; 5,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,04</t>
+          <t>0,29; 2,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,71</t>
+          <t>0,0; 2,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,58; 6,66</t>
+          <t>1,46; 6,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,75; 4,79</t>
+          <t>0,71; 4,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 6,04</t>
+          <t>1,24; 5,86</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,75</t>
+          <t>0,52; 2,75</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,36; 6,02</t>
+          <t>2,49; 6,24</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,14</t>
+          <t>1,2; 4,0</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,36</t>
+          <t>1,02; 3,46</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,86</t>
+          <t>0,0; 1,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,97</t>
+          <t>0,44; 3,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,35</t>
+          <t>0,0; 1,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,88</t>
+          <t>1,35; 5,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,74; 4,63</t>
+          <t>1,82; 4,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,66</t>
+          <t>0,59; 2,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,12</t>
+          <t>0,38; 1,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,95</t>
+          <t>1,81; 4,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,92</t>
+          <t>1,09; 2,87</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,25</t>
+          <t>0,66; 2,34</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,3</t>
+          <t>0,29; 1,42</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,82; 4,11</t>
+          <t>1,87; 4,41</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,29</t>
+          <t>0,0; 2,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 5,87</t>
+          <t>0,99; 6,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,72</t>
+          <t>0,97; 3,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,05</t>
+          <t>0,0; 2,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,58</t>
+          <t>0,91; 4,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,32</t>
+          <t>0,36; 2,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,7</t>
+          <t>1,2; 3,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,58</t>
+          <t>0,16; 1,53</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 4,32</t>
+          <t>1,29; 4,19</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,52</t>
+          <t>0,16; 1,46</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,21</t>
+          <t>1,33; 3,36</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,1</t>
+          <t>0,29; 3,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,8</t>
+          <t>0,28; 2,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 4,89</t>
+          <t>1,33; 5,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,01</t>
+          <t>0,0; 0,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,27</t>
+          <t>0,25; 2,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,75; 5,06</t>
+          <t>1,69; 5,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,37; 7,12</t>
+          <t>2,32; 6,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,46</t>
+          <t>0,61; 2,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,05</t>
+          <t>0,39; 2,1</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,35</t>
+          <t>1,15; 3,27</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,26; 5,3</t>
+          <t>2,37; 5,21</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,56</t>
+          <t>0,48; 1,51</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,85</t>
+          <t>0,39; 3,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,09; 6,58</t>
+          <t>1,53; 7,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,87</t>
+          <t>0,0; 3,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,6</t>
+          <t>0,0; 2,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,31</t>
+          <t>0,49; 4,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,34; 6,94</t>
+          <t>1,34; 6,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,68</t>
+          <t>0,47; 4,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,11</t>
+          <t>0,0; 1,05</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,16</t>
+          <t>0,51; 3,22</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,02; 5,65</t>
+          <t>1,94; 5,59</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,03</t>
+          <t>0,49; 2,84</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,19</t>
+          <t>0,11; 1,25</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,81</t>
+          <t>0,0; 1,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,05</t>
+          <t>0,72; 4,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,85</t>
+          <t>0,0; 1,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,11; 6,4</t>
+          <t>2,08; 6,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,1; 5,22</t>
+          <t>1,1; 5,25</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,43</t>
+          <t>0,34; 3,62</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,29; 5,83</t>
+          <t>2,27; 5,38</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,22</t>
+          <t>0,0; 0,89</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,75</t>
+          <t>1,23; 3,71</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,91</t>
+          <t>0,2; 1,8</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,54; 5,31</t>
+          <t>2,47; 5,28</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,68</t>
+          <t>0,28; 1,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,0</t>
+          <t>0,9; 2,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,53</t>
+          <t>0,16; 1,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,42; 6,11</t>
+          <t>2,49; 6,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,63</t>
+          <t>0,29; 1,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,31</t>
+          <t>0,72; 2,48</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,95</t>
+          <t>0,42; 1,86</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,23; 59,51</t>
+          <t>5,21; 64,02</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,29</t>
+          <t>0,38; 1,34</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,41</t>
+          <t>0,96; 2,24</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,26</t>
+          <t>0,33; 1,29</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,4; 50,18</t>
+          <t>4,34; 47,15</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,1</t>
+          <t>0,42; 2,06</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,94</t>
+          <t>0,38; 2,14</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,83</t>
+          <t>0,4; 1,85</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,42</t>
+          <t>0,54; 2,55</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,17</t>
+          <t>0,54; 2,25</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,17</t>
+          <t>1,05; 3,19</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,62</t>
+          <t>0,7; 2,49</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,07</t>
+          <t>1,26; 2,97</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,85</t>
+          <t>0,61; 1,75</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,1</t>
+          <t>0,84; 2,14</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,72; 1,84</t>
+          <t>0,69; 1,84</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,29</t>
+          <t>1,0; 2,35</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,6; 1,28</t>
+          <t>0,61; 1,31</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,34; 2,38</t>
+          <t>1,42; 2,48</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,66; 1,35</t>
+          <t>0,62; 1,36</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,78</t>
+          <t>1,54; 2,68</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,85; 1,59</t>
+          <t>0,84; 1,6</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,64; 2,67</t>
+          <t>1,67; 2,61</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,23; 2,1</t>
+          <t>1,21; 2,09</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,67; 25,54</t>
+          <t>2,69; 25,12</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,31</t>
+          <t>0,82; 1,31</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,63; 2,35</t>
+          <t>1,63; 2,33</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,02; 1,58</t>
+          <t>1,03; 1,63</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,33; 15,07</t>
+          <t>2,35; 14,49</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad psíquica</t>
+          <t>Hogares con personas con limitación por discapacidad psíquica (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1002; 11150</t>
+          <t>992; 11291</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6881; 23233</t>
+          <t>6649; 22947</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2791; 15526</t>
+          <t>3285; 15439</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1111; 9473</t>
+          <t>918; 8756</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 7076</t>
+          <t>0; 7472</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4546; 19120</t>
+          <t>4205; 18051</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2177; 13829</t>
+          <t>2054; 13675</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3536; 17501</t>
+          <t>3593; 16961</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2875; 14674</t>
+          <t>2757; 14687</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13733; 35022</t>
+          <t>14512; 36289</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6942; 24138</t>
+          <t>7001; 23308</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5823; 20223</t>
+          <t>6143; 20806</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 9158</t>
+          <t>0; 9547</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1972; 15011</t>
+          <t>2242; 15683</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 6771</t>
+          <t>0; 6337</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7387; 25310</t>
+          <t>6998; 26671</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8778; 23315</t>
+          <t>9188; 24278</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3132; 13946</t>
+          <t>3072; 14309</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2006; 11066</t>
+          <t>1965; 10218</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9443; 25477</t>
+          <t>9295; 25561</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10836; 29137</t>
+          <t>10895; 28573</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7105; 23158</t>
+          <t>6771; 24109</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2138; 13357</t>
+          <t>2972; 14518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18758; 42491</t>
+          <t>19306; 45546</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 7305</t>
+          <t>0; 7231</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3218; 19032</t>
+          <t>3202; 19688</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1820</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3044; 11772</t>
+          <t>3054; 11713</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6870</t>
+          <t>0; 7622</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3162; 15627</t>
+          <t>3090; 14420</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1761; 11176</t>
+          <t>1213; 9960</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4234; 12914</t>
+          <t>4194; 13183</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1046; 10337</t>
+          <t>1058; 10040</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8559; 28727</t>
+          <t>8558; 27893</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1061; 9943</t>
+          <t>1066; 9561</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8806; 21339</t>
+          <t>8844; 22321</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1055; 11117</t>
+          <t>1050; 11169</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1056; 10457</t>
+          <t>1053; 10368</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4632; 18086</t>
+          <t>4925; 18678</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3165</t>
+          <t>0; 3063</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>920; 8433</t>
+          <t>927; 8042</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6799; 19676</t>
+          <t>6577; 19691</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9160; 27575</t>
+          <t>8992; 26460</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3075; 11706</t>
+          <t>2923; 11750</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3273; 14952</t>
+          <t>2880; 15310</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9069; 25524</t>
+          <t>8753; 24944</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17137; 40171</t>
+          <t>17936; 39434</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3737; 12285</t>
+          <t>3754; 11937</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>800; 7818</t>
+          <t>799; 7206</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2324; 13984</t>
+          <t>3245; 14908</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 6058</t>
+          <t>0; 6676</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 4652</t>
+          <t>0; 4139</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1005; 8943</t>
+          <t>1014; 8862</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2947; 15232</t>
+          <t>2949; 14354</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1034; 10241</t>
+          <t>1020; 9924</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 2873</t>
+          <t>0; 2712</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2395; 12971</t>
+          <t>2114; 13222</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8716; 24426</t>
+          <t>8384; 24173</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2868; 13029</t>
+          <t>2090; 12220</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>492; 5227</t>
+          <t>498; 5464</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4911</t>
+          <t>0; 4243</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1990; 11107</t>
+          <t>1964; 11319</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4874</t>
+          <t>0; 5169</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5684; 17256</t>
+          <t>5611; 16996</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 1970</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3087; 14605</t>
+          <t>3083; 14698</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>922; 9369</t>
+          <t>928; 9897</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5875; 14988</t>
+          <t>5838; 13821</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 6722</t>
+          <t>0; 4898</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6255; 20770</t>
+          <t>6807; 20575</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>990; 10242</t>
+          <t>1072; 9631</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>13393; 27981</t>
+          <t>13025; 27827</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1768; 10356</t>
+          <t>1745; 10446</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>6127; 19866</t>
+          <t>5953; 19219</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1049; 10026</t>
+          <t>1044; 9924</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15118; 38168</t>
+          <t>15560; 39181</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1862; 10415</t>
+          <t>1851; 10479</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4061; 16028</t>
+          <t>4976; 17241</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2157; 13450</t>
+          <t>2876; 12858</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>44393; 505357</t>
+          <t>44247; 543684</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3973; 16164</t>
+          <t>4719; 16848</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12802; 32701</t>
+          <t>12994; 30322</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4853; 17015</t>
+          <t>4404; 17418</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>64828; 739421</t>
+          <t>64011; 694796</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>3201; 15612</t>
+          <t>3096; 15345</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2068; 15119</t>
+          <t>2927; 16647</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3140; 14269</t>
+          <t>3126; 14433</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4622; 22435</t>
+          <t>5003; 23648</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4178; 17037</t>
+          <t>4206; 17623</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>8448; 26114</t>
+          <t>8683; 26261</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5549; 21611</t>
+          <t>5792; 20546</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>9649; 22037</t>
+          <t>9023; 21327</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>9459; 28318</t>
+          <t>9310; 26694</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>13732; 33735</t>
+          <t>13545; 34353</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>11527; 29495</t>
+          <t>11073; 29536</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>16464; 37670</t>
+          <t>16522; 38626</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>19763; 41995</t>
+          <t>20150; 42995</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>46068; 81624</t>
+          <t>48781; 85110</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>22447; 45701</t>
+          <t>21114; 46130</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>55572; 96163</t>
+          <t>53415; 92622</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>28622; 53787</t>
+          <t>28386; 53962</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>58274; 95142</t>
+          <t>59306; 92986</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>43518; 74307</t>
+          <t>42883; 74139</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>99266; 948285</t>
+          <t>99799; 932453</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>53688; 87187</t>
+          <t>54557; 87362</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>113673; 164089</t>
+          <t>114140; 162553</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>70551; 109519</t>
+          <t>71741; 113052</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>166849; 1081122</t>
+          <t>168822; 1039504</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_psíq_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2A_psíq_R-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 4,14</t>
+          <t>0,37; 4,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,26; 7,79</t>
+          <t>2,33; 7,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 5,26</t>
+          <t>0,84; 4,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,81</t>
+          <t>0,53; 3,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,86</t>
+          <t>0,0; 2,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,46; 6,28</t>
+          <t>1,41; 6,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 4,74</t>
+          <t>0,75; 4,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,24; 5,86</t>
+          <t>1,19; 5,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,75</t>
+          <t>0,51; 2,78</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,49; 6,24</t>
+          <t>2,41; 5,96</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,0</t>
+          <t>1,14; 3,91</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,46</t>
+          <t>1,03; 3,28</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,94</t>
+          <t>0,0; 2,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,1</t>
+          <t>0,4; 2,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,26</t>
+          <t>0,0; 1,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 5,14</t>
+          <t>1,24; 4,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,82; 4,82</t>
+          <t>1,7; 4,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,73</t>
+          <t>0,6; 2,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,95</t>
+          <t>0,38; 2,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,81; 4,96</t>
+          <t>2,19; 5,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,87</t>
+          <t>1,08; 2,76</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,34</t>
+          <t>0,71; 2,42</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,42</t>
+          <t>0,28; 1,25</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,87; 4,41</t>
+          <t>1,98; 4,37</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,27</t>
+          <t>0,0; 1,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 6,08</t>
+          <t>1,0; 6,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,47 +1012,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,71</t>
+          <t>1,06; 4,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,27</t>
+          <t>0,0; 2,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 4,23</t>
+          <t>0,78; 4,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,96</t>
+          <t>0,27; 3,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,78</t>
+          <t>1,18; 3,81</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,53</t>
+          <t>0,16; 1,49</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 4,19</t>
+          <t>1,26; 4,27</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,46</t>
+          <t>0,16; 1,54</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,36</t>
+          <t>1,53; 3,63</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,11</t>
+          <t>0,44; 3,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,77</t>
+          <t>0,28; 2,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,33; 5,05</t>
+          <t>1,44; 5,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,98</t>
+          <t>0,0; 1,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1162,37 +1162,37 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,69; 5,06</t>
+          <t>1,69; 5,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,32; 6,83</t>
+          <t>2,54; 7,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,47</t>
+          <t>0,97; 3,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,1</t>
+          <t>0,42; 2,09</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,27</t>
+          <t>1,23; 3,27</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,37; 5,21</t>
+          <t>2,31; 5,08</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,51</t>
+          <t>0,57; 1,79</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,54</t>
+          <t>0,4; 3,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,53; 7,01</t>
+          <t>1,59; 7,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,16</t>
+          <t>0,0; 2,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,32</t>
+          <t>0,0; 2,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,27</t>
+          <t>0,49; 4,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,34; 6,54</t>
+          <t>1,45; 6,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,54</t>
+          <t>0,83; 4,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,05</t>
+          <t>0,0; 1,25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,22</t>
+          <t>0,5; 3,14</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,94; 5,59</t>
+          <t>2,01; 5,69</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,84</t>
+          <t>0,51; 2,8</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,25</t>
+          <t>0,18; 1,46</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -1417,22 +1417,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,57</t>
+          <t>0,0; 2,04</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,72; 4,13</t>
+          <t>0,71; 4,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,96</t>
+          <t>0,0; 2,11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,08; 6,3</t>
+          <t>1,88; 6,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1442,37 +1442,37 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,1; 5,25</t>
+          <t>1,09; 4,97</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,62</t>
+          <t>0,34; 3,2</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,27; 5,38</t>
+          <t>2,27; 5,7</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,89</t>
+          <t>0,0; 1,08</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,71</t>
+          <t>1,12; 3,84</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,8</t>
+          <t>0,2; 1,9</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,47; 5,28</t>
+          <t>2,68; 5,31</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -1557,22 +1557,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,7</t>
+          <t>0,27; 1,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,9</t>
+          <t>0,87; 2,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,51</t>
+          <t>0,16; 1,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,49; 6,28</t>
+          <t>2,25; 5,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1582,37 +1582,37 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,48</t>
+          <t>0,72; 2,44</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,86</t>
+          <t>0,31; 1,84</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,21; 64,02</t>
+          <t>4,62; 8,06</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,34</t>
+          <t>0,37; 1,29</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,24</t>
+          <t>0,92; 2,26</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,29</t>
+          <t>0,35; 1,3</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,34; 47,15</t>
+          <t>3,85; 6,15</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,06</t>
+          <t>0,43; 2,06</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,14</t>
+          <t>0,37; 2,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,85</t>
+          <t>0,38; 1,85</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,55</t>
+          <t>1,2; 3,14</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,25</t>
+          <t>0,53; 2,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,19</t>
+          <t>1,07; 3,3</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,49</t>
+          <t>0,72; 2,58</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,97</t>
+          <t>1,27; 2,89</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,75</t>
+          <t>0,65; 1,78</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,14</t>
+          <t>0,82; 2,06</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,84</t>
+          <t>0,72; 1,92</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,35</t>
+          <t>1,44; 2,81</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -1837,32 +1837,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,31</t>
+          <t>0,63; 1,35</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,42; 2,48</t>
+          <t>1,41; 2,43</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,36</t>
+          <t>0,64; 1,32</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,68</t>
+          <t>1,82; 2,89</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,84; 1,6</t>
+          <t>0,84; 1,64</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,67; 2,61</t>
+          <t>1,65; 2,62</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1872,27 +1872,27 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,69; 25,12</t>
+          <t>2,6; 3,62</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,31</t>
+          <t>0,79; 1,31</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,63; 2,33</t>
+          <t>1,65; 2,34</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,03; 1,63</t>
+          <t>1,03; 1,58</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,35; 14,49</t>
+          <t>2,34; 3,07</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3449</t>
+          <t>4537</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8275</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11724</t>
+          <t>12306</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>992; 11291</t>
+          <t>1008; 11275</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6649; 22947</t>
+          <t>6872; 22566</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3285; 15439</t>
+          <t>2474; 14551</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>918; 8756</t>
+          <t>1676; 10259</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 7472</t>
+          <t>0; 6456</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4205; 18051</t>
+          <t>4056; 18671</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2054; 13675</t>
+          <t>2176; 13341</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3593; 16961</t>
+          <t>3774; 15904</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2757; 14687</t>
+          <t>2749; 14859</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14512; 36289</t>
+          <t>14026; 34697</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7001; 23308</t>
+          <t>6632; 22760</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6143; 20806</t>
+          <t>6532; 20831</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13946</t>
+          <t>14220</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>15549</t>
+          <t>18192</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>29495</t>
+          <t>32412</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 9547</t>
+          <t>0; 10583</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2242; 15683</t>
+          <t>2038; 14288</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 6337</t>
+          <t>0; 7054</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6998; 26671</t>
+          <t>6593; 25373</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9188; 24278</t>
+          <t>8589; 24087</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3072; 14309</t>
+          <t>3117; 14419</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1965; 10218</t>
+          <t>1972; 11168</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9295; 25561</t>
+          <t>11977; 30212</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10895; 28573</t>
+          <t>10720; 27548</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6771; 24109</t>
+          <t>7260; 24878</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2972; 14518</t>
+          <t>2922; 12838</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19306; 45546</t>
+          <t>21306; 47052</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6499</t>
+          <t>7814</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7834</t>
+          <t>7787</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14333</t>
+          <t>15601</t>
         </is>
       </c>
     </row>
@@ -2625,12 +2625,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 7231</t>
+          <t>0; 6354</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3202; 19688</t>
+          <t>3248; 20733</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2640,47 +2640,47 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3054; 11713</t>
+          <t>3365; 14802</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 7622</t>
+          <t>0; 6716</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3090; 14420</t>
+          <t>2651; 14707</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1213; 9960</t>
+          <t>912; 10339</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4194; 13183</t>
+          <t>4210; 13582</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1058; 10040</t>
+          <t>1052; 9761</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8558; 27893</t>
+          <t>8368; 28420</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1066; 9561</t>
+          <t>1077; 10109</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8844; 22321</t>
+          <t>10296; 24377</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>1778</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6530</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>7245</t>
+          <t>8559</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1050; 11169</t>
+          <t>1568; 10932</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1053; 10368</t>
+          <t>1048; 10733</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4925; 18678</t>
+          <t>5334; 18561</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3063</t>
+          <t>0; 6890</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>927; 8042</t>
+          <t>913; 8062</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6577; 19691</t>
+          <t>6580; 19504</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8992; 26460</t>
+          <t>9832; 27848</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2923; 11750</t>
+          <t>4097; 13062</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2880; 15310</t>
+          <t>3066; 15226</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8753; 24944</t>
+          <t>9421; 24912</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17936; 39434</t>
+          <t>17470; 38471</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3754; 11937</t>
+          <t>4498; 14252</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1363</t>
+          <t>1524</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>903</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>2427</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>799; 7206</t>
+          <t>816; 7484</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3245; 14908</t>
+          <t>3373; 15485</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 6676</t>
+          <t>0; 5870</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 4139</t>
+          <t>0; 5108</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1014; 8862</t>
+          <t>1013; 9084</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2949; 14354</t>
+          <t>3187; 14485</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1020; 9924</t>
+          <t>1818; 9672</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 2712</t>
+          <t>0; 2856</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2114; 13222</t>
+          <t>2059; 12903</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8384; 24173</t>
+          <t>8688; 24582</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2090; 12220</t>
+          <t>2201; 12016</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>498; 5464</t>
+          <t>768; 6360</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10125</t>
+          <t>9772</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>9386</t>
+          <t>10043</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>19510</t>
+          <t>19815</t>
         </is>
       </c>
     </row>
@@ -3249,22 +3249,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4243</t>
+          <t>0; 5531</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1964; 11319</t>
+          <t>1936; 10967</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5169</t>
+          <t>0; 5555</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5611; 16996</t>
+          <t>5101; 16611</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3274,37 +3274,37 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3083; 14698</t>
+          <t>3060; 13904</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>928; 9897</t>
+          <t>919; 8747</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5838; 13821</t>
+          <t>5975; 15030</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 4898</t>
+          <t>0; 5902</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6807; 20575</t>
+          <t>6195; 21254</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1072; 9631</t>
+          <t>1062; 10207</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>13025; 27827</t>
+          <t>14314; 28354</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>24070</t>
+          <t>25587</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>241646</t>
+          <t>46388</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>265716</t>
+          <t>71975</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1745; 10446</t>
+          <t>1652; 11358</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>5953; 19219</t>
+          <t>5790; 19420</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1044; 9924</t>
+          <t>1047; 8995</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15560; 39181</t>
+          <t>16207; 40002</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1851; 10479</t>
+          <t>1820; 10448</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4976; 17241</t>
+          <t>5024; 16940</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2876; 12858</t>
+          <t>2111; 12754</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>44247; 543684</t>
+          <t>35639; 62210</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4719; 16848</t>
+          <t>4607; 16222</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12994; 30322</t>
+          <t>12533; 30639</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4404; 17418</t>
+          <t>4701; 17544</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>64011; 694796</t>
+          <t>57440; 91775</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>12818</t>
+          <t>15864</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>14415</t>
+          <t>16298</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>27233</t>
+          <t>32162</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>3096; 15345</t>
+          <t>3203; 15310</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2927; 16647</t>
+          <t>2892; 15682</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3126; 14433</t>
+          <t>2993; 14392</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5003; 23648</t>
+          <t>9582; 25033</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4206; 17623</t>
+          <t>4132; 17215</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>8683; 26261</t>
+          <t>8798; 27217</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5792; 20546</t>
+          <t>5982; 21290</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>9023; 21327</t>
+          <t>10585; 23988</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>9310; 26694</t>
+          <t>9871; 27135</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>13545; 34353</t>
+          <t>13165; 32961</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>11073; 29536</t>
+          <t>11610; 30866</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>16522; 38626</t>
+          <t>23430; 45852</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>72985</t>
+          <t>81098</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>304229</t>
+          <t>114160</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>377213</t>
+          <t>195258</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>20150; 42995</t>
+          <t>20555; 44210</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>48781; 85110</t>
+          <t>48481; 83120</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>21114; 46130</t>
+          <t>21819; 44714</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>53415; 92622</t>
+          <t>64472; 102248</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>28386; 53962</t>
+          <t>28524; 55457</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>59306; 92986</t>
+          <t>58689; 93319</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>42883; 74139</t>
+          <t>42859; 73940</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>99799; 932453</t>
+          <t>97053; 135221</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>54557; 87362</t>
+          <t>52846; 86909</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>114140; 162553</t>
+          <t>114989; 163756</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>71741; 113052</t>
+          <t>71447; 109788</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>168822; 1039504</t>
+          <t>170301; 223138</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_psíq_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2A_psíq_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad psíquica (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad psíquica (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad psíquica (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad psíquica (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
